--- a/paper_trading_lay0x1/sinais_legado_2026-07-16.xlsx
+++ b/paper_trading_lay0x1/sinais_legado_2026-07-16.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Sinais" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -670,8 +670,12 @@
           <t>93.6%</t>
         </is>
       </c>
-      <c r="J5" t="inlineStr"/>
-      <c r="K5" t="inlineStr"/>
+      <c r="J5" t="n">
+        <v>1</v>
+      </c>
+      <c r="K5" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -717,8 +721,12 @@
           <t>91.2%</t>
         </is>
       </c>
-      <c r="J6" t="inlineStr"/>
-      <c r="K6" t="inlineStr"/>
+      <c r="J6" t="n">
+        <v>1</v>
+      </c>
+      <c r="K6" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -1140,8 +1148,12 @@
           <t>92.9%</t>
         </is>
       </c>
-      <c r="J15" t="inlineStr"/>
-      <c r="K15" t="inlineStr"/>
+      <c r="J15" t="n">
+        <v>1</v>
+      </c>
+      <c r="K15" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
